--- a/xls/square_un_16_tri3_23.xlsx
+++ b/xls/square_un_16_tri3_23.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>741</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>340</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>598</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>3330</v>
+      </c>
+      <c r="I21">
+        <v>-8.699500730664998e-5</v>
+      </c>
+      <c r="J21">
+        <v>-0.2759252298400616</v>
+      </c>
+      <c r="K21">
+        <v>3.2582420967610948</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>741</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>668</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>3738</v>
+      </c>
+      <c r="I22">
+        <v>-7.183990397880486e-7</v>
+      </c>
+      <c r="J22">
+        <v>-0.0016740065199918504</v>
+      </c>
+      <c r="K22">
+        <v>3.0057909213059535</v>
+      </c>
+    </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
       </c>
       <c r="B23">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-2.3952192803720527</v>
+        <v>-7.207789756420052e-8</v>
       </c>
       <c r="J23">
-        <v>-1.9011438351772856</v>
+        <v>-0.00013127396163602342</v>
       </c>
       <c r="K23">
-        <v>1.0854520729089447</v>
+        <v>2.487899550575502</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.5592042503354984</v>
+        <v>-4.846445664970024e-8</v>
       </c>
       <c r="J24">
-        <v>-1.2175749405120253</v>
+        <v>-9.220543281345114e-5</v>
       </c>
       <c r="K24">
-        <v>2.2352783750646843</v>
+        <v>2.421816859566974</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.05878835348983451</v>
+        <v>-2.1865335829243606e-8</v>
       </c>
       <c r="J25">
-        <v>-0.056207281980825204</v>
+        <v>-4.2045467684289016e-5</v>
       </c>
       <c r="K25">
-        <v>3.6315263849414796</v>
+        <v>2.2564243378458757</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.00463821043841868</v>
+        <v>-1.7092681971106546e-8</v>
       </c>
       <c r="J26">
-        <v>-0.00492169144805896</v>
+        <v>-3.23296190610284e-5</v>
       </c>
       <c r="K26">
-        <v>3.292423531445241</v>
+        <v>2.1987339057912547</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.0009536469796124591</v>
+        <v>-1.2672938517952043e-8</v>
       </c>
       <c r="J27">
-        <v>-0.0009660100559871312</v>
+        <v>-2.389842967129806e-5</v>
       </c>
       <c r="K27">
-        <v>2.9432275000936965</v>
+        <v>2.132872952109922</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-0.0003339871061580192</v>
+        <v>-9.869485702236764e-9</v>
       </c>
       <c r="J28">
-        <v>-0.00039917934784211486</v>
+        <v>-1.857977642661336e-5</v>
       </c>
       <c r="K28">
-        <v>2.7872841310721563</v>
+        <v>2.0787524103887165</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-0.000229008499798277</v>
+        <v>-9.289244838310276e-9</v>
       </c>
       <c r="J29">
-        <v>-0.00026185648117770384</v>
+        <v>-1.8283605443301272e-5</v>
       </c>
       <c r="K29">
-        <v>2.6872239753038722</v>
+        <v>2.0790983830888004</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-0.0001423163994444215</v>
+        <v>-6.397569725172843e-9</v>
       </c>
       <c r="J30">
-        <v>-0.00016800215900298439</v>
+        <v>-1.2417276432874104e-5</v>
       </c>
       <c r="K30">
-        <v>2.6003137290645175</v>
+        <v>1.9936130231817364</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-0.00011112930830448051</v>
+        <v>-5.503442826898674e-9</v>
       </c>
       <c r="J31">
-        <v>-0.00012827693523607928</v>
+        <v>-1.0793067998709473e-5</v>
       </c>
       <c r="K31">
-        <v>2.5356398037128036</v>
+        <v>1.9651627753569054</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>677</v>
+        <v>741</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-8.938616057389759e-5</v>
+        <v>-4.916485572573945e-9</v>
       </c>
       <c r="J32">
-        <v>-0.00010304929292487302</v>
+        <v>-9.616458730261965e-6</v>
       </c>
       <c r="K32">
-        <v>2.4882017748435605</v>
+        <v>1.9394839274348863</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_23.xlsx
+++ b/xls/square_un_16_tri3_23.xlsx
@@ -482,13 +482,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-8.699500730664998e-5</v>
+        <v>-1.9256317878876137</v>
       </c>
       <c r="J21">
-        <v>-0.2759252298400616</v>
+        <v>-1.5627471653597524</v>
       </c>
       <c r="K21">
-        <v>3.2582420967610948</v>
+        <v>1.0372693569952922</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-7.183990397880486e-7</v>
+        <v>-0.538821676532404</v>
       </c>
       <c r="J22">
-        <v>-0.0016740065199918504</v>
+        <v>-0.4660257710328042</v>
       </c>
       <c r="K22">
-        <v>3.0057909213059535</v>
+        <v>2.5393109411665584</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-7.207789756420052e-8</v>
+        <v>-0.00027500976276216555</v>
       </c>
       <c r="J23">
-        <v>-0.00013127396163602342</v>
+        <v>-0.00028326725133231414</v>
       </c>
       <c r="K23">
-        <v>2.487899550575502</v>
+        <v>2.6838534200607724</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-4.846445664970024e-8</v>
+        <v>-0.0001423283995161688</v>
       </c>
       <c r="J24">
-        <v>-9.220543281345114e-5</v>
+        <v>-0.00013972732397232005</v>
       </c>
       <c r="K24">
-        <v>2.421816859566974</v>
+        <v>2.5119216214094213</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-2.1865335829243606e-8</v>
+        <v>-5.4949308196032793e-5</v>
       </c>
       <c r="J25">
-        <v>-4.2045467684289016e-5</v>
+        <v>-5.2654095859321824e-5</v>
       </c>
       <c r="K25">
-        <v>2.2564243378458757</v>
+        <v>2.295544090270699</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.7092681971106546e-8</v>
+        <v>-2.917071261567807e-5</v>
       </c>
       <c r="J26">
-        <v>-3.23296190610284e-5</v>
+        <v>-3.261360462484271e-5</v>
       </c>
       <c r="K26">
-        <v>2.1987339057912547</v>
+        <v>2.2316183147418323</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.2672938517952043e-8</v>
+        <v>-2.734257186535856e-5</v>
       </c>
       <c r="J27">
-        <v>-2.389842967129806e-5</v>
+        <v>-2.641267844232575e-5</v>
       </c>
       <c r="K27">
-        <v>2.132872952109922</v>
+        <v>2.15113032334334</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-9.869485702236764e-9</v>
+        <v>-2.6849097897533135e-5</v>
       </c>
       <c r="J28">
-        <v>-1.857977642661336e-5</v>
+        <v>-2.4014403364557397e-5</v>
       </c>
       <c r="K28">
-        <v>2.0787524103887165</v>
+        <v>2.106815330543807</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -762,13 +762,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-9.289244838310276e-9</v>
+        <v>-2.19567113668413e-5</v>
       </c>
       <c r="J29">
-        <v>-1.8283605443301272e-5</v>
+        <v>-2.0987966571623935e-5</v>
       </c>
       <c r="K29">
-        <v>2.0790983830888004</v>
+        <v>2.095339989132733</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -797,13 +797,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-6.397569725172843e-9</v>
+        <v>-1.3116814062721022e-5</v>
       </c>
       <c r="J30">
-        <v>-1.2417276432874104e-5</v>
+        <v>-1.3212717911612856e-5</v>
       </c>
       <c r="K30">
-        <v>1.9936130231817364</v>
+        <v>2.0092832610249314</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -832,13 +832,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-5.503442826898674e-9</v>
+        <v>-1.2522813292795561e-5</v>
       </c>
       <c r="J31">
-        <v>-1.0793067998709473e-5</v>
+        <v>-1.2058288533167596e-5</v>
       </c>
       <c r="K31">
-        <v>1.9651627753569054</v>
+        <v>1.977750058348366</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -867,13 +867,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-4.916485572573945e-9</v>
+        <v>-1.0880314757648637e-5</v>
       </c>
       <c r="J32">
-        <v>-9.616458730261965e-6</v>
+        <v>-1.0527240425221e-5</v>
       </c>
       <c r="K32">
-        <v>1.9394839274348863</v>
+        <v>1.9492633754549422</v>
       </c>
     </row>
   </sheetData>
